--- a/knockout-example-small.xlsx
+++ b/knockout-example-small.xlsx
@@ -181,10 +181,10 @@
     <t>Round 1 - Match 2</t>
   </si>
   <si>
-    <t>Round 1 - Match 3</t>
-  </si>
-  <si>
-    <t>Round 1 - Match 4</t>
+    <t>Round 2 - Match 3</t>
+  </si>
+  <si>
+    <t>Round 2 - Match 4</t>
   </si>
   <si>
     <t>Round 2 - Match 5</t>
@@ -1254,7 +1254,7 @@
     </row>
     <row r="4">
       <c r="A4" s="19" t="str">
-        <f>'data'!$B$4</f>
+        <f>'data'!$B$7</f>
       </c>
       <c r="B4" s="19"/>
       <c r="C4" s="19"/>
@@ -1262,7 +1262,7 @@
       <c r="E4" s="19"/>
       <c r="F4" s="19"/>
       <c r="G4" s="19" t="str">
-        <f>'data'!$B$3</f>
+        <f>'data'!$B$6</f>
       </c>
     </row>
     <row r="5">
@@ -1332,7 +1332,7 @@
     </row>
     <row r="11">
       <c r="A11" s="19" t="str">
-        <f>'data'!$B$4</f>
+        <f>'data'!$B$7</f>
       </c>
       <c r="B11" s="19" t="s">
         <v>46</v>
@@ -1348,7 +1348,7 @@
         <v>46</v>
       </c>
       <c r="G11" s="19" t="str">
-        <f>'data'!$B$3</f>
+        <f>'data'!$B$6</f>
       </c>
     </row>
     <row r="12">
@@ -1408,7 +1408,7 @@
     </row>
     <row r="20">
       <c r="A20" s="19" t="str">
-        <f>'data'!$B$7</f>
+        <f>'data'!$B$12</f>
       </c>
       <c r="B20" s="19"/>
       <c r="C20" s="19"/>
@@ -1416,7 +1416,7 @@
       <c r="E20" s="19"/>
       <c r="F20" s="19"/>
       <c r="G20" s="19" t="str">
-        <f>'data'!$B$6</f>
+        <f>'data'!$B$11</f>
       </c>
     </row>
     <row r="21">
@@ -1486,7 +1486,7 @@
     </row>
     <row r="27">
       <c r="A27" s="19" t="str">
-        <f>'data'!$B$7</f>
+        <f>'data'!$B$12</f>
       </c>
       <c r="B27" s="19" t="s">
         <v>46</v>
@@ -1502,7 +1502,7 @@
         <v>46</v>
       </c>
       <c r="G27" s="19" t="str">
-        <f>'data'!$B$6</f>
+        <f>'data'!$B$11</f>
       </c>
     </row>
     <row r="28">
@@ -1538,313 +1538,313 @@
       </c>
       <c r="G32" s="23"/>
     </row>
-    <row r="34">
-      <c r="A34" s="11" t="s">
+    <row r="39">
+      <c r="A39" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="B34" s="11"/>
-      <c r="C34" s="11"/>
-      <c r="D34" s="11"/>
-      <c r="E34" s="11"/>
-      <c r="F34" s="11"/>
-      <c r="G34" s="11"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="21" t="s">
+      <c r="B39" s="11"/>
+      <c r="C39" s="11"/>
+      <c r="D39" s="11"/>
+      <c r="E39" s="11"/>
+      <c r="F39" s="11"/>
+      <c r="G39" s="11"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="21" t="s">
         <v>43</v>
       </c>
-      <c r="D35" s="19" t="s">
+      <c r="D40" s="19" t="s">
         <v>44</v>
       </c>
-      <c r="G35" s="20" t="s">
+      <c r="G40" s="20" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="19" t="str">
-        <f>'data'!$B$9</f>
-      </c>
-      <c r="B36" s="19"/>
-      <c r="C36" s="19"/>
-      <c r="D36" s="22"/>
-      <c r="E36" s="19"/>
-      <c r="F36" s="19"/>
-      <c r="G36" s="19" t="str">
-        <f>'data'!$B$8</f>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="19">
+    <row r="41">
+      <c r="A41" s="19" t="str">
+        <f>'data'!$B$4</f>
+      </c>
+      <c r="B41" s="19"/>
+      <c r="C41" s="19"/>
+      <c r="D41" s="22"/>
+      <c r="E41" s="19"/>
+      <c r="F41" s="19"/>
+      <c r="G41" s="19" t="str">
+        <f>'data'!$B$3</f>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="19">
         <v>1</v>
       </c>
-      <c r="B37" s="22"/>
-      <c r="C37" s="22"/>
-      <c r="D37" s="22"/>
-      <c r="E37" s="22"/>
-      <c r="F37" s="22"/>
-      <c r="G37" s="19">
+      <c r="B42" s="22"/>
+      <c r="C42" s="22"/>
+      <c r="D42" s="22"/>
+      <c r="E42" s="22"/>
+      <c r="F42" s="22"/>
+      <c r="G42" s="19">
         <v>1</v>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="19">
+    <row r="43">
+      <c r="A43" s="19">
         <v>2</v>
       </c>
-      <c r="B38" s="22"/>
-      <c r="C38" s="22"/>
-      <c r="D38" s="22"/>
-      <c r="E38" s="22"/>
-      <c r="F38" s="22"/>
-      <c r="G38" s="19">
+      <c r="B43" s="22"/>
+      <c r="C43" s="22"/>
+      <c r="D43" s="22"/>
+      <c r="E43" s="22"/>
+      <c r="F43" s="22"/>
+      <c r="G43" s="19">
         <v>2</v>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="19">
+    <row r="44">
+      <c r="A44" s="19">
         <v>3</v>
       </c>
-      <c r="B39" s="22"/>
-      <c r="C39" s="22"/>
-      <c r="D39" s="22"/>
-      <c r="E39" s="22"/>
-      <c r="F39" s="22"/>
-      <c r="G39" s="19">
+      <c r="B44" s="22"/>
+      <c r="C44" s="22"/>
+      <c r="D44" s="22"/>
+      <c r="E44" s="22"/>
+      <c r="F44" s="22"/>
+      <c r="G44" s="19">
         <v>3</v>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="19">
+    <row r="45">
+      <c r="A45" s="19">
         <v>4</v>
       </c>
-      <c r="B40" s="22"/>
-      <c r="C40" s="22"/>
-      <c r="D40" s="22"/>
-      <c r="E40" s="22"/>
-      <c r="F40" s="22"/>
-      <c r="G40" s="19">
+      <c r="B45" s="22"/>
+      <c r="C45" s="22"/>
+      <c r="D45" s="22"/>
+      <c r="E45" s="22"/>
+      <c r="F45" s="22"/>
+      <c r="G45" s="19">
         <v>4</v>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="19">
+    <row r="46">
+      <c r="A46" s="19">
         <v>5</v>
       </c>
-      <c r="B41" s="22"/>
-      <c r="C41" s="22"/>
-      <c r="D41" s="22"/>
-      <c r="E41" s="22"/>
-      <c r="F41" s="22"/>
-      <c r="G41" s="19">
+      <c r="B46" s="22"/>
+      <c r="C46" s="22"/>
+      <c r="D46" s="22"/>
+      <c r="E46" s="22"/>
+      <c r="F46" s="22"/>
+      <c r="G46" s="19">
         <v>5</v>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="19" t="str">
-        <f>'data'!$B$9</f>
-      </c>
-      <c r="B43" s="19" t="s">
+    <row r="48">
+      <c r="A48" s="19" t="str">
+        <f>'data'!$B$4</f>
+      </c>
+      <c r="B48" s="19" t="s">
         <v>46</v>
       </c>
-      <c r="C43" s="19" t="s">
+      <c r="C48" s="19" t="s">
         <v>47</v>
       </c>
-      <c r="D43" s="19"/>
-      <c r="E43" s="19" t="s">
+      <c r="D48" s="19"/>
+      <c r="E48" s="19" t="s">
         <v>47</v>
       </c>
-      <c r="F43" s="19" t="s">
+      <c r="F48" s="19" t="s">
         <v>46</v>
       </c>
-      <c r="G43" s="19" t="str">
-        <f>'data'!$B$8</f>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="19" t="s">
+      <c r="G48" s="19" t="str">
+        <f>'data'!$B$3</f>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="19" t="s">
         <v>48</v>
       </c>
-      <c r="B44" s="19" t="str">
-        <f>IF(UPPER(D37)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B37," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C37," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E37," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F37," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D38)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C38," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F38," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D39)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B39," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C39," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E39," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F39," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D40)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B40," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C40," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E40," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F40," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D41)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B41," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C41," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E41," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F41," ",""),"0",""),"-",""))),1,0))</f>
-      </c>
-      <c r="C44" s="19" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B37," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C37," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B39," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C39," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B40," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C40," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B41," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C41," ",""),"0",""),"-",""))</f>
-      </c>
-      <c r="D44" s="19"/>
-      <c r="E44" s="19" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E37," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F37," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E39," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F39," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E40," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F40," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E41," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F41," ",""),"0",""),"-",""))</f>
-      </c>
-      <c r="F44" s="19" t="str">
-        <f>IF(UPPER(D37)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E37," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F37," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B37," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C37," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D38)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F38," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C38," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D39)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E39," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F39," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B39," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C39," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D40)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E40," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F40," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B40," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C40," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D41)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E41," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F41," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B41," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C41," ",""),"0",""),"-",""))),1,0))</f>
-      </c>
-      <c r="G44" s="19" t="s">
+      <c r="B49" s="19" t="str">
+        <f>IF(UPPER(D42)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B42," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C42," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E42," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F42," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D43)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B43," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C43," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E43," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F43," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D44)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B44," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C44," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E44," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F44," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D45)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B45," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C45," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E45," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F45," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D46)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B46," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C46," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E46," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F46," ",""),"0",""),"-",""))),1,0))</f>
+      </c>
+      <c r="C49" s="19" t="str">
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B42," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C42," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B43," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C43," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B44," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C44," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B45," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C45," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B46," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C46," ",""),"0",""),"-",""))</f>
+      </c>
+      <c r="D49" s="19"/>
+      <c r="E49" s="19" t="str">
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E42," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F42," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E43," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F43," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E44," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F44," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E45," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F45," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E46," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F46," ",""),"0",""),"-",""))</f>
+      </c>
+      <c r="F49" s="19" t="str">
+        <f>IF(UPPER(D42)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E42," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F42," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B42," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C42," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D43)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E43," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F43," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B43," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C43," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D44)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E44," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F44," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B44," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C44," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D45)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E45," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F45," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B45," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C45," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D46)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E46," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F46," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B46," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C46," ",""),"0",""),"-",""))),1,0))</f>
+      </c>
+      <c r="G49" s="19" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="47">
-      <c r="F47" t="s">
+    <row r="52">
+      <c r="F52" t="s">
         <v>49</v>
       </c>
-      <c r="G47" s="23"/>
-    </row>
-    <row r="48">
-      <c r="F48" t="s">
+      <c r="G52" s="23"/>
+    </row>
+    <row r="53">
+      <c r="F53" t="s">
         <v>50</v>
       </c>
-      <c r="G48" s="23"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="11" t="s">
+      <c r="G53" s="23"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="11" t="s">
         <v>53</v>
       </c>
-      <c r="B50" s="11"/>
-      <c r="C50" s="11"/>
-      <c r="D50" s="11"/>
-      <c r="E50" s="11"/>
-      <c r="F50" s="11"/>
-      <c r="G50" s="11"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="21" t="s">
+      <c r="B55" s="11"/>
+      <c r="C55" s="11"/>
+      <c r="D55" s="11"/>
+      <c r="E55" s="11"/>
+      <c r="F55" s="11"/>
+      <c r="G55" s="11"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="21" t="s">
         <v>43</v>
       </c>
-      <c r="D51" s="19" t="s">
+      <c r="D56" s="19" t="s">
         <v>44</v>
       </c>
-      <c r="G51" s="20" t="s">
+      <c r="G56" s="20" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="19" t="str">
-        <f>'data'!$B$12</f>
-      </c>
-      <c r="B52" s="19"/>
-      <c r="C52" s="19"/>
-      <c r="D52" s="22"/>
-      <c r="E52" s="19"/>
-      <c r="F52" s="19"/>
-      <c r="G52" s="19" t="str">
-        <f>'data'!$B$11</f>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="19">
+    <row r="57">
+      <c r="A57" s="19" t="str">
+        <f>CONCATENATE("M 1 ",G15)</f>
+      </c>
+      <c r="B57" s="19"/>
+      <c r="C57" s="19"/>
+      <c r="D57" s="22"/>
+      <c r="E57" s="19"/>
+      <c r="F57" s="19"/>
+      <c r="G57" s="19" t="str">
+        <f>'data'!$B$5</f>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="19">
         <v>1</v>
       </c>
-      <c r="B53" s="22"/>
-      <c r="C53" s="22"/>
-      <c r="D53" s="22"/>
-      <c r="E53" s="22"/>
-      <c r="F53" s="22"/>
-      <c r="G53" s="19">
+      <c r="B58" s="22"/>
+      <c r="C58" s="22"/>
+      <c r="D58" s="22"/>
+      <c r="E58" s="22"/>
+      <c r="F58" s="22"/>
+      <c r="G58" s="19">
         <v>1</v>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="19">
+    <row r="59">
+      <c r="A59" s="19">
         <v>2</v>
       </c>
-      <c r="B54" s="22"/>
-      <c r="C54" s="22"/>
-      <c r="D54" s="22"/>
-      <c r="E54" s="22"/>
-      <c r="F54" s="22"/>
-      <c r="G54" s="19">
+      <c r="B59" s="22"/>
+      <c r="C59" s="22"/>
+      <c r="D59" s="22"/>
+      <c r="E59" s="22"/>
+      <c r="F59" s="22"/>
+      <c r="G59" s="19">
         <v>2</v>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="19">
+    <row r="60">
+      <c r="A60" s="19">
         <v>3</v>
       </c>
-      <c r="B55" s="22"/>
-      <c r="C55" s="22"/>
-      <c r="D55" s="22"/>
-      <c r="E55" s="22"/>
-      <c r="F55" s="22"/>
-      <c r="G55" s="19">
+      <c r="B60" s="22"/>
+      <c r="C60" s="22"/>
+      <c r="D60" s="22"/>
+      <c r="E60" s="22"/>
+      <c r="F60" s="22"/>
+      <c r="G60" s="19">
         <v>3</v>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="19">
+    <row r="61">
+      <c r="A61" s="19">
         <v>4</v>
       </c>
-      <c r="B56" s="22"/>
-      <c r="C56" s="22"/>
-      <c r="D56" s="22"/>
-      <c r="E56" s="22"/>
-      <c r="F56" s="22"/>
-      <c r="G56" s="19">
+      <c r="B61" s="22"/>
+      <c r="C61" s="22"/>
+      <c r="D61" s="22"/>
+      <c r="E61" s="22"/>
+      <c r="F61" s="22"/>
+      <c r="G61" s="19">
         <v>4</v>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="19">
+    <row r="62">
+      <c r="A62" s="19">
         <v>5</v>
       </c>
-      <c r="B57" s="22"/>
-      <c r="C57" s="22"/>
-      <c r="D57" s="22"/>
-      <c r="E57" s="22"/>
-      <c r="F57" s="22"/>
-      <c r="G57" s="19">
+      <c r="B62" s="22"/>
+      <c r="C62" s="22"/>
+      <c r="D62" s="22"/>
+      <c r="E62" s="22"/>
+      <c r="F62" s="22"/>
+      <c r="G62" s="19">
         <v>5</v>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="19" t="str">
-        <f>'data'!$B$12</f>
-      </c>
-      <c r="B59" s="19" t="s">
+    <row r="64">
+      <c r="A64" s="19" t="str">
+        <f>CONCATENATE("M 1 ",G15)</f>
+      </c>
+      <c r="B64" s="19" t="s">
         <v>46</v>
       </c>
-      <c r="C59" s="19" t="s">
+      <c r="C64" s="19" t="s">
         <v>47</v>
       </c>
-      <c r="D59" s="19"/>
-      <c r="E59" s="19" t="s">
+      <c r="D64" s="19"/>
+      <c r="E64" s="19" t="s">
         <v>47</v>
       </c>
-      <c r="F59" s="19" t="s">
+      <c r="F64" s="19" t="s">
         <v>46</v>
       </c>
-      <c r="G59" s="19" t="str">
-        <f>'data'!$B$11</f>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="19" t="s">
+      <c r="G64" s="19" t="str">
+        <f>'data'!$B$5</f>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="19" t="s">
         <v>48</v>
       </c>
-      <c r="B60" s="19" t="str">
-        <f>IF(UPPER(D53)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B53," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C53," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E53," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F53," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D54)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B54," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C54," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E54," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F54," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D55)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B55," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C55," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E55," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F55," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D56)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B56," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C56," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E56," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F56," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D57)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B57," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C57," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E57," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F57," ",""),"0",""),"-",""))),1,0))</f>
-      </c>
-      <c r="C60" s="19" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B53," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C53," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B54," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C54," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B55," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C55," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B56," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C56," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B57," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C57," ",""),"0",""),"-",""))</f>
-      </c>
-      <c r="D60" s="19"/>
-      <c r="E60" s="19" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E53," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F53," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E54," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F54," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E55," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F55," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E56," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F56," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E57," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F57," ",""),"0",""),"-",""))</f>
-      </c>
-      <c r="F60" s="19" t="str">
-        <f>IF(UPPER(D53)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E53," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F53," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B53," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C53," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D54)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E54," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F54," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B54," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C54," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D55)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E55," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F55," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B55," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C55," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D56)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E56," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F56," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B56," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C56," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D57)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E57," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F57," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B57," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C57," ",""),"0",""),"-",""))),1,0))</f>
-      </c>
-      <c r="G60" s="19" t="s">
+      <c r="B65" s="19" t="str">
+        <f>IF(UPPER(D58)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B58," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C58," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E58," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F58," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D59)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B59," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C59," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E59," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F59," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D60)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B60," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C60," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E60," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F60," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D61)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B61," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C61," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E61," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F61," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D62)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B62," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C62," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E62," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F62," ",""),"0",""),"-",""))),1,0))</f>
+      </c>
+      <c r="C65" s="19" t="str">
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B58," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C58," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B59," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C59," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B60," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C60," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B61," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C61," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B62," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C62," ",""),"0",""),"-",""))</f>
+      </c>
+      <c r="D65" s="19"/>
+      <c r="E65" s="19" t="str">
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E58," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F58," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E59," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F59," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E60," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F60," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E61," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F61," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E62," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F62," ",""),"0",""),"-",""))</f>
+      </c>
+      <c r="F65" s="19" t="str">
+        <f>IF(UPPER(D58)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E58," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F58," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B58," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C58," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D59)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E59," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F59," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B59," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C59," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D60)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E60," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F60," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B60," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C60," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D61)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E61," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F61," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B61," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C61," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D62)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E62," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F62," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B62," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C62," ",""),"0",""),"-",""))),1,0))</f>
+      </c>
+      <c r="G65" s="19" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="63">
-      <c r="F63" t="s">
+    <row r="68">
+      <c r="F68" t="s">
         <v>49</v>
       </c>
-      <c r="G63" s="23"/>
-    </row>
-    <row r="64">
-      <c r="F64" t="s">
+      <c r="G68" s="23"/>
+    </row>
+    <row r="69">
+      <c r="F69" t="s">
         <v>50</v>
       </c>
-      <c r="G64" s="23"/>
+      <c r="G69" s="23"/>
     </row>
     <row r="71">
       <c r="A71" s="11" t="s">
@@ -1870,7 +1870,7 @@
     </row>
     <row r="73">
       <c r="A73" s="19" t="str">
-        <f>CONCATENATE("M 2 ",G31)</f>
+        <f>'data'!$B$9</f>
       </c>
       <c r="B73" s="19"/>
       <c r="C73" s="19"/>
@@ -1878,7 +1878,7 @@
       <c r="E73" s="19"/>
       <c r="F73" s="19"/>
       <c r="G73" s="19" t="str">
-        <f>'data'!$B$5</f>
+        <f>'data'!$B$8</f>
       </c>
     </row>
     <row r="74">
@@ -1948,7 +1948,7 @@
     </row>
     <row r="80">
       <c r="A80" s="19" t="str">
-        <f>CONCATENATE("M 2 ",G31)</f>
+        <f>'data'!$B$9</f>
       </c>
       <c r="B80" s="19" t="s">
         <v>46</v>
@@ -1964,7 +1964,7 @@
         <v>46</v>
       </c>
       <c r="G80" s="19" t="str">
-        <f>'data'!$B$5</f>
+        <f>'data'!$B$8</f>
       </c>
     </row>
     <row r="81">
@@ -2024,7 +2024,7 @@
     </row>
     <row r="89">
       <c r="A89" s="19" t="str">
-        <f>CONCATENATE("M 4 ",G63)</f>
+        <f>CONCATENATE("M 2 ",G31)</f>
       </c>
       <c r="B89" s="19"/>
       <c r="C89" s="19"/>
@@ -2102,7 +2102,7 @@
     </row>
     <row r="96">
       <c r="A96" s="19" t="str">
-        <f>CONCATENATE("M 4 ",G63)</f>
+        <f>CONCATENATE("M 2 ",G31)</f>
       </c>
       <c r="B96" s="19" t="s">
         <v>46</v>
@@ -2178,7 +2178,7 @@
     </row>
     <row r="110">
       <c r="A110" s="19" t="str">
-        <f>CONCATENATE("M 5 ",G84)</f>
+        <f>CONCATENATE("M 4 ",G68)</f>
       </c>
       <c r="B110" s="19"/>
       <c r="C110" s="19"/>
@@ -2186,7 +2186,7 @@
       <c r="E110" s="19"/>
       <c r="F110" s="19"/>
       <c r="G110" s="19" t="str">
-        <f>CONCATENATE("M 1 ",G15)</f>
+        <f>CONCATENATE("M 3 ",G52)</f>
       </c>
     </row>
     <row r="111">
@@ -2256,7 +2256,7 @@
     </row>
     <row r="117">
       <c r="A117" s="19" t="str">
-        <f>CONCATENATE("M 5 ",G84)</f>
+        <f>CONCATENATE("M 4 ",G68)</f>
       </c>
       <c r="B117" s="19" t="s">
         <v>46</v>
@@ -2272,7 +2272,7 @@
         <v>46</v>
       </c>
       <c r="G117" s="19" t="str">
-        <f>CONCATENATE("M 1 ",G15)</f>
+        <f>CONCATENATE("M 3 ",G52)</f>
       </c>
     </row>
     <row r="118">
@@ -2340,7 +2340,7 @@
       <c r="E126" s="19"/>
       <c r="F126" s="19"/>
       <c r="G126" s="19" t="str">
-        <f>CONCATENATE("M 3 ",G47)</f>
+        <f>CONCATENATE("M 5 ",G84)</f>
       </c>
     </row>
     <row r="127">
@@ -2426,7 +2426,7 @@
         <v>46</v>
       </c>
       <c r="G133" s="19" t="str">
-        <f>CONCATENATE("M 3 ",G47)</f>
+        <f>CONCATENATE("M 5 ",G84)</f>
       </c>
     </row>
     <row r="134">
@@ -2622,8 +2622,8 @@
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A18:G18"/>
-    <mergeCell ref="A34:G34"/>
-    <mergeCell ref="A50:G50"/>
+    <mergeCell ref="A39:G39"/>
+    <mergeCell ref="A55:G55"/>
     <mergeCell ref="A71:G71"/>
     <mergeCell ref="A87:G87"/>
     <mergeCell ref="A108:G108"/>
@@ -2633,7 +2633,7 @@
   <printOptions horizontalCentered="true" verticalCentered="true"/>
   <pageSetup fitToHeight="0" fitToWidth="1" orientation="portrait" pageOrder="downThenOver" paperSize="9"/>
   <rowBreaks count="4" manualBreakCount="4">
-    <brk id="33" max="16383" man="true"/>
+    <brk id="38" max="16383" man="true"/>
     <brk id="70" max="16383" man="true"/>
     <brk id="107" max="16383" man="true"/>
     <brk id="144" max="16383" man="true"/>
@@ -2671,29 +2671,35 @@
       <c r="J1" s="11"/>
       <c r="K1" s="11"/>
     </row>
-    <row r="5">
-      <c r="C5" s="16" t="s">
+    <row r="6">
+      <c r="C6" s="16"/>
+      <c r="D6" s="16"/>
+      <c r="E6" s="16" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="6">
-      <c r="D6" s="14"/>
-      <c r="E6" s="13">
-        <v>1</v>
-      </c>
-    </row>
     <row r="7">
-      <c r="C7" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="D7" s="15"/>
-      <c r="E7" s="12"/>
+      <c r="F7" s="14"/>
+      <c r="G7" s="12"/>
+    </row>
+    <row r="8">
+      <c r="G8" s="13">
+        <v>3</v>
+      </c>
     </row>
     <row r="9">
+      <c r="G9" s="12"/>
       <c r="H9" s="14"/>
       <c r="I9" s="12"/>
     </row>
     <row r="10">
+      <c r="C10" s="16"/>
+      <c r="D10" s="16"/>
+      <c r="E10" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="F10" s="15"/>
+      <c r="G10" s="12"/>
       <c r="I10" s="12"/>
     </row>
     <row r="11">
@@ -2726,7 +2732,7 @@
     </row>
     <row r="16">
       <c r="G16" s="13">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H16" s="15"/>
       <c r="I16" s="12"/>
@@ -2742,7 +2748,7 @@
     <row r="18">
       <c r="D18" s="14"/>
       <c r="E18" s="13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F18" s="15"/>
       <c r="G18" s="12"/>
@@ -2762,35 +2768,41 @@
       </c>
     </row>
     <row r="21">
-      <c r="C21" s="16" t="s">
+      <c r="K21" s="12"/>
+    </row>
+    <row r="22">
+      <c r="C22" s="16"/>
+      <c r="D22" s="16"/>
+      <c r="E22" s="16" t="s">
         <v>31</v>
       </c>
-      <c r="K21" s="12"/>
-    </row>
-    <row r="22">
-      <c r="D22" s="14"/>
-      <c r="E22" s="13">
-        <v>3</v>
-      </c>
       <c r="K22" s="12"/>
     </row>
     <row r="23">
-      <c r="C23" s="16" t="s">
-        <v>33</v>
-      </c>
-      <c r="D23" s="15"/>
-      <c r="E23" s="12"/>
+      <c r="F23" s="14"/>
+      <c r="G23" s="12"/>
       <c r="K23" s="12"/>
     </row>
     <row r="24">
+      <c r="G24" s="13">
+        <v>5</v>
+      </c>
       <c r="K24" s="12"/>
     </row>
     <row r="25">
+      <c r="G25" s="12"/>
       <c r="H25" s="14"/>
       <c r="I25" s="12"/>
       <c r="K25" s="12"/>
     </row>
     <row r="26">
+      <c r="C26" s="16"/>
+      <c r="D26" s="16"/>
+      <c r="E26" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="F26" s="15"/>
+      <c r="G26" s="12"/>
       <c r="I26" s="12"/>
       <c r="K26" s="12"/>
     </row>
@@ -2837,7 +2849,7 @@
     <row r="34">
       <c r="D34" s="14"/>
       <c r="E34" s="13">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F34" s="15"/>
       <c r="G34" s="12"/>

--- a/knockout-example-small.xlsx
+++ b/knockout-example-small.xlsx
@@ -233,79 +233,79 @@
   </numFmts>
   <fonts count="11">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
     </font>
     <font>
+      <b val="1"/>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <b val="1"/>
-      <color rgb="FF000000"/>
-      <sz val="12"/>
     </font>
     <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color rgb="FF000000"/>
-      <sz val="12"/>
     </font>
     <font>
+      <b val="1"/>
+      <u val="single"/>
+      <sz val="16"/>
+      <color/>
       <name val="Calibri"/>
       <family val="2"/>
-      <b val="1"/>
-      <color/>
-      <sz val="16"/>
-      <u val="single"/>
     </font>
     <font>
+      <b val="1"/>
+      <u val="single"/>
+      <sz val="12"/>
+      <color/>
       <name val="Calibri"/>
       <family val="2"/>
-      <b val="1"/>
-      <color/>
-      <sz val="12"/>
-      <u val="single"/>
     </font>
     <font>
+      <sz val="12"/>
+      <color/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color/>
-      <sz val="12"/>
     </font>
     <font>
+      <b val="1"/>
+      <sz val="28"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <b val="1"/>
-      <color rgb="FF000000"/>
-      <sz val="28"/>
     </font>
     <font>
+      <b val="1"/>
+      <sz val="72"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <b val="1"/>
-      <color rgb="FF000000"/>
-      <sz val="72"/>
     </font>
     <font>
+      <b val="1"/>
+      <sz val="100"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <b val="1"/>
-      <color rgb="FF000000"/>
-      <sz val="100"/>
     </font>
     <font>
+      <sz val="110"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color rgb="FF000000"/>
-      <sz val="110"/>
     </font>
     <font>
+      <b val="1"/>
+      <sz val="12"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <b val="1"/>
-      <color rgb="FFFFFFFF"/>
-      <sz val="12"/>
     </font>
   </fonts>
   <fills count="5">
@@ -974,16 +974,16 @@
         <v>0</v>
       </c>
       <c r="D2" s="3">
-        <v>0.0020833333333333333</v>
+        <v>0.00208333333333333</v>
       </c>
       <c r="E2" s="3" t="str">
         <f>(A2*B2*C2*D2)</f>
       </c>
       <c r="F2" s="3">
-        <v>0.00034722222222222224</v>
+        <v>0.000347222222222222</v>
       </c>
       <c r="G2" s="3">
-        <v>0.020833333333333332</v>
+        <v>0.0208333333333333</v>
       </c>
       <c r="H2" s="24" t="str">
         <f>C2*I2+J2</f>
@@ -1000,16 +1000,16 @@
         <v>0</v>
       </c>
       <c r="D3" s="3">
-        <v>0.0020833333333333333</v>
+        <v>0.00208333333333333</v>
       </c>
       <c r="E3" s="3" t="str">
         <f>(A3*B3*C3*D3)</f>
       </c>
       <c r="F3" s="3">
-        <v>0.00034722222222222224</v>
+        <v>0.000347222222222222</v>
       </c>
       <c r="G3" s="3">
-        <v>0.020833333333333332</v>
+        <v>0.0208333333333333</v>
       </c>
       <c r="H3" s="3" t="str">
         <f>E3+(A3*C3*F3)+G3</f>
@@ -1078,16 +1078,16 @@
       </c>
       <c r="C8" s="2"/>
       <c r="D8" s="3">
-        <v>0.002777777777777778</v>
+        <v>0.00277777777777777</v>
       </c>
       <c r="E8" s="3" t="str">
         <f>(A8*B8*D8)</f>
       </c>
       <c r="F8" s="3">
-        <v>0.00034722222222222224</v>
+        <v>0.000347222222222222</v>
       </c>
       <c r="G8" s="3">
-        <v>0.020833333333333332</v>
+        <v>0.0208333333333333</v>
       </c>
       <c r="H8" s="24" t="str">
         <f>E8+(A8*F8)+G8</f>
